--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,13 +454,23 @@
           <t>xstd</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>xcv_lo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>xcv_hi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2044692561999378</v>
+        <v>0.1172736391675514</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -469,10 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.037162789557563</v>
+        <v>0.93125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05940660187439515</v>
+        <v>0.01792151097300547</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.85078125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.02421875</v>
       </c>
     </row>
     <row r="3">
@@ -480,19 +496,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08960640148091052</v>
+        <v>0.07679252962271826</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7955307438000622</v>
+        <v>0.71875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.90227078095043</v>
+        <v>0.80625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09262812017371054</v>
+        <v>0.02366211810750114</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.69453125</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.93046875</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05523753598774355</v>
+        <v>0.04368650217706826</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7059243423191517</v>
+        <v>0.5625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8934412785199759</v>
+        <v>0.790625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09918474065347449</v>
+        <v>0.01617101530860419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7015625</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.84375</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +548,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04765113438267984</v>
+        <v>0.04265441057893889</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6506868063314081</v>
+        <v>0.46875</v>
       </c>
       <c r="E5" t="n">
-        <v>1.006295471811673</v>
+        <v>0.803125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1138910807229336</v>
+        <v>0.01979166666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7015625</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +574,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0458420280181716</v>
+        <v>0.0395327942497754</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5553845375660484</v>
+        <v>0.40625</v>
       </c>
       <c r="E6" t="n">
-        <v>1.004788031186916</v>
+        <v>0.81875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1198188034956582</v>
+        <v>0.02901747557746691</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9375</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +600,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03714817994282157</v>
+        <v>0.03773584905660378</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5095425095478768</v>
+        <v>0.375</v>
       </c>
       <c r="E7" t="n">
-        <v>1.013138803801467</v>
+        <v>0.83125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1213450422089981</v>
+        <v>0.0284128785353872</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.69453125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9375</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +626,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03379934280465176</v>
+        <v>0.0358490566037736</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4723943296050553</v>
+        <v>0.34375</v>
       </c>
       <c r="E8" t="n">
-        <v>1.048646695618463</v>
+        <v>0.828125</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1247312052440396</v>
+        <v>0.02765816259864948</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7015625</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9375</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +652,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.032357450416569</v>
+        <v>0.0180817610062893</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4385949868004035</v>
+        <v>0.25</v>
       </c>
       <c r="E9" t="n">
-        <v>1.061575441847637</v>
+        <v>0.834375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1260297427619533</v>
+        <v>0.02467233183818127</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.72578125</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9546875</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +678,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02531555607182848</v>
+        <v>0.01467505241090146</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4062375363838345</v>
+        <v>0.21875</v>
       </c>
       <c r="E10" t="n">
-        <v>1.077418792575618</v>
+        <v>0.853125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1270062380174611</v>
+        <v>0.02510827248582072</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.96875</v>
       </c>
     </row>
     <row r="11">
@@ -640,19 +704,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02443952229084503</v>
+        <v>0.01415094339622642</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>0.380921980312006</v>
+        <v>0.21875</v>
       </c>
       <c r="E11" t="n">
-        <v>1.101133376295486</v>
+        <v>0.85625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1300730008708544</v>
+        <v>0.02384483987970749</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.75703125</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.96875</v>
       </c>
     </row>
     <row r="12">
@@ -660,19 +730,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0213637353298299</v>
+        <v>0.009433962264150945</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3564824580211611</v>
+        <v>0.21875</v>
       </c>
       <c r="E12" t="n">
-        <v>1.11745185287957</v>
+        <v>0.84375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.130252703958744</v>
+        <v>0.02134781409574917</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.75703125</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.96171875</v>
       </c>
     </row>
     <row r="13">
@@ -680,179 +756,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01791831513384259</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3351187226913311</v>
+        <v>0.21875</v>
       </c>
       <c r="E13" t="n">
-        <v>1.134313802577869</v>
+        <v>0.84375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1313745890137428</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.01708929645087926</v>
-      </c>
-      <c r="C14" t="n">
-        <v>13</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3172004075574885</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.142749367840877</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.1320842657667172</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.01655382869420443</v>
-      </c>
-      <c r="C15" t="n">
-        <v>14</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3001111111066092</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.148491866285587</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.1325574139696839</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.009340798513014149</v>
-      </c>
-      <c r="C16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2835572824124048</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.166190711268744</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.133183028216744</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.00613220473648225</v>
-      </c>
-      <c r="C17" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2742164838993906</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.162126518981567</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1331973729584567</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.001725867138077568</v>
-      </c>
-      <c r="C18" t="n">
-        <v>17</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2680842791629083</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.163051510668807</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.1335828664231596</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.0008627336582958962</v>
-      </c>
-      <c r="C19" t="n">
-        <v>18</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2663584120248308</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.168432140191379</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.1338894543647986</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.0007091507542807241</v>
-      </c>
-      <c r="C20" t="n">
-        <v>19</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.265495678366535</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.16906555101618</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.1336908496554017</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.2647865276122542</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.171070667684017</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.1342430420330504</v>
+        <v>0.02134781409574917</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.75703125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.96171875</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
@@ -446,22 +446,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>xerror</t>
+          <t>CV error</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>xstd</t>
+          <t>CV std</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>xcv_lo</t>
+          <t>CV lo</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>xcv_hi</t>
+          <t>CV hi</t>
         </is>
       </c>
     </row>
